--- a/output/看屋檢查清單_新北建案_2026-10-09_五_環境風險.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-10-09_五_環境風險.xlsx
@@ -231,7 +231,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）</t>
+          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）；實登：ToEstate(至2026-07)</t>
         </is>
       </c>
     </row>
@@ -723,53 +723,56 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>591 170筆/76萬；樂屋網 170筆/73.7萬；5168記326筆（口徑不同）
-另一平台記近6月均69.9萬：最新2026-06 78.6萬、最高2026-01 88.0萬、最低2026-05 63.3萬
-+永慶統計列新北近一年熱銷中古社區第2名
-!591/樂屋網仍停在170筆</t>
+          <t>ToEstate：近1年58筆中位71.9萬(年減5%)；近3年192筆76.2萬
+1房83筆中位78.5萬(約12.4坪/993萬)；2房74.8萬；3房68.4萬
+最新1房：2026-06 13.2坪1,038萬(78.6萬)
+!2026年大坪數成交多，均價下修</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>591 176筆/67萬（近一年67.5萬）；樂屋網 176筆/69.1萬；PLEX 175筆；樂居一年67.11萬
-成交區間59.0~72.8萬/坪；最新2026-07-03 1房17.74坪69.1萬（總價1,227萬）
-平台收斂於67~69.1萬，可信</t>
+          <t>ToEstate預售175筆(2025-05~2026-07)：中位66.2萬、近6月68.4萬
+1房30筆中位68.0萬(17.1坪/1,199萬)；2房66.0萬；3房64.1萬
+最新2026-07 1房17.74坪1,227萬(69.1萬)
++新店區預售中位88.1萬，本案相對低</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>全案：591 554筆/67萬；樂屋網 596筆/66萬；5168一年67.9萬；永慶近1年62萬
-!分期價差大，勿用全案均價議價：
-II紐約公園 591 146筆/67萬、5168記73.2萬；III巴黎公園 樂屋網182筆/85.1萬（上週168筆/79.9萬）、樂居83.13萬
-!2026-09單筆58.3萬/坪屬個案</t>
+          <t>ToEstate：II紐約公園近1年中位67.7萬(全期298筆)，2025~26成交66~69萬
+III巴黎公園預售182筆，近24月83.4萬、近6月85.4萬
+4英倫公園預售173筆中位85.1萬
+!分期價差逾15萬，看屋先確認期別</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>591 329筆/近1年75.2萬（更新至2026-08，最新75.4、區間67.7~85.3萬）
-台北房地王 357筆/75.9萬（08-20）；樂居/5168一年76.6萬；樂屋網 335筆/79.7萬偏高
-!平台落差4.5萬，逐筆比對再議</t>
+          <t>ToEstate預售357筆(2024-07~2026-08)：中位75.4萬、近6月77.3萬
+1房102筆中位77.8萬(16.2坪/1,431萬)；2房73.6萬；3房74.5萬
+樓層：2~5F 73.4萬→16F以上79.5萬；車位中位180萬</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>!四平台收斂：591 231筆/88.9萬(09-21)、5168一年89.0萬(09-29)、信義近半年88.9萬、樂居一年88.29萬
-樂屋網231筆/88.9萬
-成交區間65.55~103.47萬/坪</t>
+          <t>ToEstate社區228筆：近1年中位89.7萬、近3年91.2萬
+1房27筆中位89.2萬(12.9坪/1,210萬)
+2026成交：1月90.6萬、4月88.9萬、6月91.2萬(12.9坪1,180萬)
+!近1年僅4筆，量少</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>!實登筆數增加：591 16筆/82萬；樂屋網 14筆（近3月85.4萬）；台北房地王 12筆/83.0萬
-成交76.4~90.9萬；最新2026-07 1房15.65坪84.7萬（總價1,326萬）
-均價低於開價86~91萬，議價空間約2~7%</t>
+          <t>ToEstate預售14筆(2025-11~2026-07)：中位82.9萬、近6月83.5萬
+1房9筆中位83.5萬(15.7坪/1,326萬)；2房82.1萬
+最新2026-07 1房14.99坪1,252萬(83.5萬)
+!僅3筆含車位(中位260萬)</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>591 1,138筆/75.6萬；樂屋網 1,131筆/75.9萬；5168一年76.0萬；住展近一年73.6萬
-2026-07~08成交77~81萬（07-31 16F 3房81萬、8月78.5萬），剩餘戶不多
-+筆數逾千，七案中行情最透明</t>
+          <t>ToEstate預售1,084筆：全期中位61.2萬(2023早鳥價)、近24月75.2萬、近6月78.5萬
+2房531筆中位60.5萬(18.2坪)；3房553筆62.1萬(全期)
+2026-07~08成交77.4~81.0萬(3房28.5坪,含裝潢傢俱)；車位中位255萬</t>
         </is>
       </c>
     </row>
